--- a/Indomie Clients Details/Sweera.xlsx
+++ b/Indomie Clients Details/Sweera.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34FBE8E-DEE9-4440-9D30-70EC47E07CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69BF26F-F014-4452-A188-CAE3FD73C416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'1'!$K$3:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'2'!$A$1:$Q$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -3339,7 +3340,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3367,7 +3368,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -3618,7 +3619,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -3674,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -3736,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -4574,7 +4575,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4602,7 +4603,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4853,7 +4854,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -4909,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -4971,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -5809,7 +5810,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5837,7 +5838,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -6088,7 +6089,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -6144,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -6206,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -7044,7 +7045,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7072,7 +7073,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7323,7 +7324,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -7379,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -7441,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -8279,7 +8280,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8307,7 +8308,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8558,7 +8559,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -8614,7 +8615,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -8676,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -9514,7 +9515,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9542,7 +9543,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9793,7 +9794,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -9849,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -9911,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -10746,7 +10747,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10774,7 +10775,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11025,7 +11026,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -11081,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -11143,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -11977,7 +11978,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -12005,7 +12006,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -12256,7 +12257,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -12312,7 +12313,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -12374,7 +12375,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -13208,7 +13209,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13236,7 +13237,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13487,7 +13488,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -13543,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -13605,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -14439,7 +14440,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14467,7 +14468,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14718,7 +14719,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -14774,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -14836,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -18420,7 +18421,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18448,7 +18449,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18699,7 +18700,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -18755,7 +18756,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -18817,7 +18818,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -19651,7 +19652,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19679,7 +19680,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19930,7 +19931,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -19986,7 +19987,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -20048,7 +20049,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -20882,7 +20883,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20910,7 +20911,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21161,7 +21162,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -21217,7 +21218,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -21279,7 +21280,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -22113,7 +22114,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22141,7 +22142,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -22392,7 +22393,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -22448,7 +22449,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -22510,7 +22511,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -23349,7 +23350,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23377,7 +23378,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23588,7 +23589,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>36163.1524212</v>
+        <v>34738.905495600004</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23641,7 +23642,7 @@
       </c>
       <c r="U15" s="163">
         <f>+'2'!P35</f>
-        <v>49136.518933200001</v>
+        <v>47407.507305299994</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23682,7 +23683,7 @@
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" s="171">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23690,23 +23691,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>671.52</v>
+        <v>1007.28</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>7722.48</v>
+        <v>7386.72</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>1390.0463999999999</v>
+        <v>1367.3825999999999</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>45.562631999999994</v>
+        <v>43.770513000000008</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>9158.089031999998</v>
+        <v>8797.8731129999996</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23756,7 +23757,7 @@
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" s="171">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23764,23 +23765,23 @@
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>671.52</v>
+        <v>1007.28</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>7722.48</v>
+        <v>7386.72</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>1390.0463999999999</v>
+        <v>1367.3825999999999</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>45.562631999999994</v>
+        <v>43.770513000000008</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>9158.089031999998</v>
+        <v>8797.8731129999996</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -23830,7 +23831,7 @@
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18" s="171">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -23838,23 +23839,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>1175.1599999999999</v>
+        <v>1762.7399999999998</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>13514.34</v>
+        <v>12926.76</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>2432.5812000000001</v>
+        <v>2421.2492999999999</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>79.734605999999985</v>
+        <v>76.740046500000005</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>16026.655806000001</v>
+        <v>15424.749346499999</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -23900,7 +23901,7 @@
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="171">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
@@ -23908,23 +23909,23 @@
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>929.79200000000003</v>
+        <v>1394.6879999999999</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>10692.608</v>
+        <v>10227.712</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1924.6694399999999</v>
+        <v>1893.2889599999999</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>63.086387199999997</v>
+        <v>60.605004799999996</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>12680.363827200001</v>
+        <v>12181.605964799999</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -23970,7 +23971,7 @@
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K20" s="171">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23978,23 +23979,23 @@
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>929.79200000000003</v>
+        <v>1394.6879999999999</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>10692.608</v>
+        <v>10227.712</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1924.6694399999999</v>
+        <v>1893.2889599999999</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>63.086387199999997</v>
+        <v>60.605004799999996</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>12680.363827200001</v>
+        <v>12181.605964799999</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24040,7 +24041,7 @@
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K21" s="171">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -24048,23 +24049,23 @@
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>1627.136</v>
+        <v>2440.7039999999997</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>18712.064000000002</v>
+        <v>17898.495999999999</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>3368.1715199999999</v>
+        <v>3352.4812799999995</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>110.4011776</v>
+        <v>106.2548864</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>22190.636697600003</v>
+        <v>21357.232166399997</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24311,7 +24312,7 @@
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
@@ -24319,23 +24320,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>6161.84</v>
+        <v>9164.2999999999993</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>71928.216</v>
+        <v>68925.755999999994</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>12947.078880000001</v>
+        <v>12811.96818</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>424.37647439999995</v>
+        <v>408.68862089999999</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>85299.671354400009</v>
+        <v>82146.412800899998</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24465,7 +24466,7 @@
       </c>
       <c r="U30" s="164">
         <f>SUM(U14:U28)</f>
-        <v>85299.671354399994</v>
+        <v>82146.412800899998</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24519,7 +24520,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="152">
         <f>L25</f>
-        <v>6161.84</v>
+        <v>9164.2999999999993</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24562,7 +24563,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="152">
         <f>P32-P33-P34</f>
-        <v>71928.216</v>
+        <v>68925.755999999994</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24587,7 +24588,7 @@
       </c>
       <c r="P36" s="152">
         <f>N25</f>
-        <v>12947.078880000001</v>
+        <v>12811.96818</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24609,7 +24610,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="152">
         <f>P35+P36</f>
-        <v>84875.294880000001</v>
+        <v>81737.72417999999</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24634,7 +24635,7 @@
       </c>
       <c r="P38" s="152">
         <f>O38*P37</f>
-        <v>2121.882372</v>
+        <v>2043.4431044999999</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24644,7 +24645,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="159">
         <f>P37+P38</f>
-        <v>86997.177251999994</v>
+        <v>83781.167284499985</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24816,7 +24817,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24844,7 +24845,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25095,7 +25096,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -25151,24 +25152,24 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
-        <v>335.76</v>
+        <f>I16*12%</f>
+        <v>503.64</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3861.24</v>
+        <v>3693.36</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>695.02319999999997</v>
+        <v>664.8048</v>
       </c>
       <c r="O16" s="106">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>22.781315999999997</v>
+        <v>21.790824000000004</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>4579.044515999999</v>
+        <v>4379.9556240000002</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -25213,24 +25214,24 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="5">I17*8%</f>
-        <v>335.76</v>
+        <f t="shared" ref="L17:L21" si="5">I17*12%</f>
+        <v>503.64</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
-        <v>3861.24</v>
+        <v>3693.36</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>695.02319999999997</v>
+        <v>664.8048</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" si="1"/>
-        <v>22.781315999999997</v>
+        <v>21.790824000000004</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="2"/>
-        <v>4579.044515999999</v>
+        <v>4379.9556240000002</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25276,23 +25277,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>335.76</v>
+        <v>503.64</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>3861.24</v>
+        <v>3693.36</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>695.02319999999997</v>
+        <v>664.8048</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>22.781315999999997</v>
+        <v>21.790824000000004</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>4579.044515999999</v>
+        <v>4379.9556240000002</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25334,23 +25335,23 @@
       </c>
       <c r="L19" s="104">
         <f t="shared" si="5"/>
-        <v>464.89600000000002</v>
+        <v>697.34399999999994</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="6"/>
-        <v>5346.3040000000001</v>
+        <v>5113.8559999999998</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>962.33471999999995</v>
+        <v>920.49407999999994</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>31.543193599999999</v>
+        <v>30.171750400000001</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>6340.1819136000004</v>
+        <v>6064.5218304</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25392,23 +25393,23 @@
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>464.89600000000002</v>
+        <v>697.34399999999994</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>5346.3040000000001</v>
+        <v>5113.8559999999998</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>962.33471999999995</v>
+        <v>920.49407999999994</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>31.543193599999999</v>
+        <v>30.171750400000001</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>6340.1819136000004</v>
+        <v>6064.5218304</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25450,23 +25451,23 @@
       </c>
       <c r="L21" s="104">
         <f t="shared" si="5"/>
-        <v>464.89600000000002</v>
+        <v>697.34399999999994</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="6"/>
-        <v>5346.3040000000001</v>
+        <v>5113.8559999999998</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>962.33471999999995</v>
+        <v>920.49407999999994</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>31.543193599999999</v>
+        <v>30.171750400000001</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>6340.1819136000004</v>
+        <v>6064.5218304</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25667,23 +25668,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>2558.8879999999999</v>
+        <v>3759.8720000000003</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>30494.267999999996</v>
+        <v>29293.284</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>5488.9682399999992</v>
+        <v>5272.7911199999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>179.91618119999998</v>
+        <v>172.83037560000005</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>36163.1524212</v>
+        <v>34738.905495600004</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25754,7 +25755,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2558.8879999999999</v>
+        <v>3759.8720000000003</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25797,7 +25798,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>30494.268</v>
+        <v>29293.284</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25822,7 +25823,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>5488.9682399999992</v>
+        <v>5272.7911199999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25844,7 +25845,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>35983.236239999998</v>
+        <v>34566.075120000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25869,7 +25870,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>179.91618119999998</v>
+        <v>172.8303756</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25879,7 +25880,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>36163.1524212</v>
+        <v>34738.905495600004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25997,7 +25998,7 @@
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="10" style="69" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
@@ -26051,7 +26052,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -26079,7 +26080,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26330,7 +26331,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -26380,30 +26381,32 @@
         <f>(G16*D16)*F16+H16*F16</f>
         <v>4197</v>
       </c>
-      <c r="J16" s="102"/>
+      <c r="J16" s="102">
+        <v>4</v>
+      </c>
       <c r="K16" s="103">
         <f>I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
-        <v>335.76</v>
+        <f>I16*12%</f>
+        <v>503.64</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3861.24</v>
+        <v>3693.36</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>695.02319999999997</v>
+        <v>702.57780000000002</v>
       </c>
       <c r="O16" s="106">
         <f>(N16+M16)*$O$15</f>
-        <v>22.781315999999997</v>
+        <v>21.979689</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>4579.044515999999</v>
+        <v>4417.9174889999995</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -26442,30 +26445,32 @@
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
         <v>4197</v>
       </c>
-      <c r="J17" s="116"/>
+      <c r="J17" s="116">
+        <v>4</v>
+      </c>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>335.76</v>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
+        <v>503.64</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>3861.24</v>
+        <v>3693.36</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>695.02319999999997</v>
+        <v>702.57780000000002</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>22.781315999999997</v>
+        <v>21.979689</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="1"/>
-        <v>4579.044515999999</v>
+        <v>4417.9174889999995</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -26504,30 +26509,32 @@
         <f t="shared" si="2"/>
         <v>10492.5</v>
       </c>
-      <c r="J18" s="116"/>
+      <c r="J18" s="116">
+        <v>10</v>
+      </c>
       <c r="K18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>839.4</v>
+        <v>1259.0999999999999</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>9653.1</v>
+        <v>9233.4</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>1737.558</v>
+        <v>1756.4444999999998</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>56.953289999999996</v>
+        <v>54.949222499999998</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>11447.611289999999</v>
+        <v>11044.793722499999</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26562,30 +26569,32 @@
         <f t="shared" si="2"/>
         <v>5811.2</v>
       </c>
-      <c r="J19" s="116"/>
+      <c r="J19" s="116">
+        <v>4</v>
+      </c>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="104">
         <f t="shared" si="4"/>
-        <v>464.89600000000002</v>
+        <v>697.34399999999994</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="5"/>
-        <v>5346.3040000000001</v>
+        <v>5113.8559999999998</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>962.33471999999995</v>
+        <v>972.79487999999992</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="6"/>
-        <v>31.543193599999999</v>
+        <v>30.433254399999996</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="1"/>
-        <v>6340.1819136000004</v>
+        <v>6117.0841343999991</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26620,30 +26629,32 @@
         <f t="shared" si="2"/>
         <v>5811.2</v>
       </c>
-      <c r="J20" s="116"/>
+      <c r="J20" s="116">
+        <v>4</v>
+      </c>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="104">
         <f t="shared" si="4"/>
-        <v>464.89600000000002</v>
+        <v>697.34399999999994</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="5"/>
-        <v>5346.3040000000001</v>
+        <v>5113.8559999999998</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>962.33471999999995</v>
+        <v>972.79487999999992</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="6"/>
-        <v>31.543193599999999</v>
+        <v>30.433254399999996</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="1"/>
-        <v>6340.1819136000004</v>
+        <v>6117.0841343999991</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26678,30 +26689,32 @@
         <f t="shared" si="2"/>
         <v>14528</v>
       </c>
-      <c r="J21" s="116"/>
+      <c r="J21" s="116">
+        <v>10</v>
+      </c>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="104">
         <f t="shared" si="4"/>
-        <v>1162.24</v>
+        <v>1743.36</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="5"/>
-        <v>13365.76</v>
+        <v>12784.64</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>2405.8368</v>
+        <v>2431.9871999999996</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="6"/>
-        <v>78.857984000000002</v>
+        <v>76.083135999999996</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="1"/>
-        <v>15850.454784</v>
+        <v>15292.710335999998</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26902,23 +26915,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>3602.9520000000002</v>
+        <v>5404.4279999999999</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>41433.948000000004</v>
+        <v>39632.471999999994</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>7458.1106399999999</v>
+        <v>7539.1770599999982</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>244.46029319999997</v>
+        <v>235.85824529999999</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>49136.518933200001</v>
+        <v>47407.507305299994</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26989,7 +27002,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>3602.9520000000002</v>
+        <v>5404.4279999999999</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27032,7 +27045,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>41433.948000000004</v>
+        <v>39632.472000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27057,7 +27070,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>7458.1106399999999</v>
+        <v>7539.1770599999982</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27079,7 +27092,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>48892.058640000003</v>
+        <v>47171.649059999996</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27104,7 +27117,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>244.46029320000002</v>
+        <v>235.85824529999999</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27114,7 +27127,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>49136.518933200001</v>
+        <v>47407.507305299994</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27194,7 +27207,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="82" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -27286,7 +27299,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27314,7 +27327,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27565,7 +27578,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -27621,7 +27634,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -27683,7 +27696,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -28520,7 +28533,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28548,7 +28561,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28799,7 +28812,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -28855,7 +28868,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -28917,7 +28930,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -29755,7 +29768,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29783,7 +29796,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30034,7 +30047,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -30090,7 +30103,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -30152,7 +30165,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
@@ -30990,7 +31003,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -31018,7 +31031,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -31269,7 +31282,7 @@
         <v>79</v>
       </c>
       <c r="L15" s="182">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="M15" s="250"/>
       <c r="N15" s="91">
@@ -31325,7 +31338,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="104">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="105">
@@ -31387,7 +31400,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">

--- a/Indomie Clients Details/Sweera.xlsx
+++ b/Indomie Clients Details/Sweera.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69BF26F-F014-4452-A188-CAE3FD73C416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF69B465-878A-43DF-AF9E-F17B9213E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3340,7 +3340,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3368,7 +3368,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4575,7 +4575,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4603,7 +4603,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5810,7 +5810,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5838,7 +5838,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7045,7 +7045,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7073,7 +7073,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8280,7 +8280,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8308,7 +8308,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9515,7 +9515,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9543,7 +9543,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10747,7 +10747,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10775,7 +10775,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11978,7 +11978,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -12006,7 +12006,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13209,7 +13209,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13237,7 +13237,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14440,7 +14440,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14468,7 +14468,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18421,7 +18421,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18449,7 +18449,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19652,7 +19652,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19680,7 +19680,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20883,7 +20883,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20911,7 +20911,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -22114,7 +22114,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22142,7 +22142,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23350,7 +23350,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23378,7 +23378,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24817,7 +24817,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24845,7 +24845,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26052,7 +26052,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -26080,7 +26080,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26942,7 +26942,10 @@
       <c r="E26" s="144"/>
       <c r="F26" s="144"/>
       <c r="G26" s="145"/>
-      <c r="H26" s="145"/>
+      <c r="H26" s="145">
+        <f>H25/40</f>
+        <v>18</v>
+      </c>
       <c r="I26" s="146"/>
       <c r="K26" s="147"/>
       <c r="L26" s="147"/>
@@ -27299,7 +27302,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27327,7 +27330,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28533,7 +28536,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28561,7 +28564,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29768,7 +29771,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29796,7 +29799,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -31003,7 +31006,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -31031,7 +31034,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>

--- a/Indomie Clients Details/Sweera.xlsx
+++ b/Indomie Clients Details/Sweera.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A94D32F-5DAE-4AAD-B716-C69258CE532D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6B6A93-65C0-4BD3-95ED-72224DA5824C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3340,7 +3340,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -3368,7 +3368,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -4575,7 +4575,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -4603,7 +4603,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -5810,7 +5810,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -5838,7 +5838,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -7045,7 +7045,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -7073,7 +7073,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -8280,7 +8280,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -8308,7 +8308,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -9515,7 +9515,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -9543,7 +9543,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -10747,7 +10747,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -10775,7 +10775,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -11978,7 +11978,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -12006,7 +12006,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -13209,7 +13209,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -13237,7 +13237,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -14440,7 +14440,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -14468,7 +14468,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -18421,7 +18421,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -18449,7 +18449,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -19652,7 +19652,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -19680,7 +19680,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -20883,7 +20883,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -20911,7 +20911,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -22114,7 +22114,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -22142,7 +22142,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23350,7 +23350,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -23378,7 +23378,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -24817,7 +24817,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -24845,7 +24845,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -26052,7 +26052,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -26080,7 +26080,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -26942,10 +26942,7 @@
       <c r="E26" s="144"/>
       <c r="F26" s="144"/>
       <c r="G26" s="145"/>
-      <c r="H26" s="145">
-        <f>H25/40</f>
-        <v>18</v>
-      </c>
+      <c r="H26" s="145"/>
       <c r="I26" s="146"/>
       <c r="K26" s="147"/>
       <c r="L26" s="147"/>
@@ -27302,7 +27299,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -27330,7 +27327,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -28536,7 +28533,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -28564,7 +28561,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -29771,7 +29768,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -29799,7 +29796,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -31006,7 +31003,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -31034,7 +31031,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
